--- a/phys5v48hw/hw4/output/asyncLorentz/asyncLorentzCat.xlsx
+++ b/phys5v48hw/hw4/output/asyncLorentz/asyncLorentzCat.xlsx
@@ -1,52 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -65,13 +47,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -150,7 +199,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -185,7 +233,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -220,16 +267,20 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -351,80 +402,448 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1:H1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" t="str">
-        <v>Problem Size (n)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Bins</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Nodes</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Ranks</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Threads Per Rank</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Runtime</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Peak Memory</v>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Problem Size (n)</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Bins</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Ranks</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Threads Per Rank</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Runtime</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Peak Memory</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.529987089335918</v>
+      </c>
+      <c r="H2" t="n">
+        <v>140824</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C3" t="n">
+        <v>100</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.444251174107194</v>
+      </c>
+      <c r="H3" t="n">
+        <v>141060</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.459728951565921</v>
+      </c>
+      <c r="H4" t="n">
+        <v>140796</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C5" t="n">
+        <v>10</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.48496988043189</v>
+      </c>
+      <c r="H5" t="n">
+        <v>140820</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C6" t="n">
+        <v>100</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.447627434507012</v>
+      </c>
+      <c r="H6" t="n">
+        <v>141332</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.430273515172303</v>
+      </c>
+      <c r="H7" t="n">
+        <v>141116</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C8" t="n">
+        <v>10</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.468488277867436</v>
+      </c>
+      <c r="H8" t="n">
+        <v>140492</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C9" t="n">
+        <v>100</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.430536544881761</v>
+      </c>
+      <c r="H9" t="n">
+        <v>140544</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.455748470500112</v>
+      </c>
+      <c r="H10" t="n">
+        <v>141056</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C11" t="n">
+        <v>10</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" t="n">
+        <v>8</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.470564786344767</v>
+      </c>
+      <c r="H11" t="n">
+        <v>141084</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C12" t="n">
+        <v>100</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" t="n">
+        <v>8</v>
+      </c>
+      <c r="F12" t="n">
+        <v>4</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.444110928103328</v>
+      </c>
+      <c r="H12" t="n">
+        <v>141116</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" t="n">
+        <v>8</v>
+      </c>
+      <c r="F13" t="n">
+        <v>4</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.40458363853395</v>
+      </c>
+      <c r="H13" t="n">
+        <v>141776</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C14" t="n">
+        <v>10</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" t="n">
+        <v>16</v>
+      </c>
+      <c r="F14" t="n">
+        <v>8</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.463829785585403</v>
+      </c>
+      <c r="H14" t="n">
+        <v>140732</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C15" t="n">
+        <v>100</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" t="n">
+        <v>16</v>
+      </c>
+      <c r="F15" t="n">
+        <v>8</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.434639092534781</v>
+      </c>
+      <c r="H15" t="n">
+        <v>141416</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="n">
+        <v>16</v>
+      </c>
+      <c r="F16" t="n">
+        <v>8</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.358143012970686</v>
+      </c>
+      <c r="H16" t="n">
+        <v>141264</v>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="B1:H1"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/phys5v48hw/hw4/output/asyncLorentz/asyncLorentzCat.xlsx
+++ b/phys5v48hw/hw4/output/asyncLorentz/asyncLorentzCat.xlsx
@@ -1,79 +1,3 @@
-
-<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
-  <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-  </sheets>
-</workbook>
-</file>
-
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
-<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-  </fonts>
-  <fills count="2">
-    <fill>
-      <patternFill patternType="none"/>
-    </fill>
-    <fill>
-      <patternFill patternType="gray125"/>
-    </fill>
-  </fills>
-  <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-  </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-  </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-  </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-  </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
-</styleSheet>
-</file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
@@ -150,7 +74,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -185,7 +108,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -220,16 +142,20 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -351,80 +277,7 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
-</file>
-
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1:H1"/>
-  <sheetData>
-    <row r="1">
-      <c r="B1" t="str">
-        <v>Problem Size (n)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Bins</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Nodes</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Ranks</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Threads Per Rank</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Runtime</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Peak Memory</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="B1:H1"/>
-  </ignoredErrors>
-</worksheet>
 </file>
--- a/phys5v48hw/hw4/output/asyncLorentz/asyncLorentzCat.xlsx
+++ b/phys5v48hw/hw4/output/asyncLorentz/asyncLorentzCat.xlsx
@@ -1,3 +1,79 @@
+
+<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr codeName="ThisWorkbook"/>
+  <sheets>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+  </sheets>
+</workbook>
+</file>
+
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
+  <fonts count="1">
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+  </fonts>
+  <fills count="2">
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+  </fills>
+  <borders count="1">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+  </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+</styleSheet>
+</file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
@@ -74,6 +150,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -108,6 +185,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -142,20 +220,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -277,7 +351,106 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
+</file>
+
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H2"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="str">
+        <v>Problem Size (n)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Bins</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Nodes</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Ranks</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Threads Per Rank</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Runtime</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Peak Memory</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>0</v>
+      </c>
+      <c r="B2" t="str">
+        <v>1000</v>
+      </c>
+      <c r="C2" t="str">
+        <v>10</v>
+      </c>
+      <c r="D2" t="str">
+        <v>2</v>
+      </c>
+      <c r="E2" t="str">
+        <v>1</v>
+      </c>
+      <c r="F2" t="str">
+        <v>10</v>
+      </c>
+      <c r="G2" t="str">
+        <v>0.005477304</v>
+      </c>
+      <c r="H2" t="str">
+        <v>87560</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:H2"/>
+  </ignoredErrors>
+</worksheet>
 </file>
--- a/phys5v48hw/hw4/output/asyncLorentz/asyncLorentzCat.xlsx
+++ b/phys5v48hw/hw4/output/asyncLorentz/asyncLorentzCat.xlsx
@@ -1,52 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -65,13 +47,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -150,7 +199,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -185,7 +233,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -220,16 +267,20 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -351,106 +402,2268 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H86"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" t="str">
-        <v>Problem Size (n)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Bins</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Nodes</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Ranks</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Threads Per Rank</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Runtime</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Peak Memory</v>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Problem Size (n)</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Bins</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Ranks</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Threads Per Rank</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Runtime</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Peak Memory</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
+      <c r="A2" t="n">
         <v>0</v>
       </c>
-      <c r="B2" t="str">
-        <v>1000</v>
-      </c>
-      <c r="C2" t="str">
-        <v>10</v>
-      </c>
-      <c r="D2" t="str">
-        <v>2</v>
-      </c>
-      <c r="E2" t="str">
+      <c r="B2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
         <v>1</v>
       </c>
-      <c r="F2" t="str">
-        <v>10</v>
-      </c>
-      <c r="G2" t="str">
+      <c r="F2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" t="n">
         <v>0.005477304</v>
       </c>
-      <c r="H2" t="str">
+      <c r="H2" t="n">
         <v>87560</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.764500864781439</v>
+      </c>
+      <c r="H3" t="n">
+        <v>316724</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C4" t="n">
+        <v>100</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.683325862511992</v>
+      </c>
+      <c r="H4" t="n">
+        <v>318512</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.70395871065557</v>
+      </c>
+      <c r="H5" t="n">
+        <v>316852</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.770700687542558</v>
+      </c>
+      <c r="H6" t="n">
+        <v>199720</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C7" t="n">
+        <v>100</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.775364259257913</v>
+      </c>
+      <c r="H7" t="n">
+        <v>199928</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.72805071156472</v>
+      </c>
+      <c r="H8" t="n">
+        <v>199744</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C9" t="n">
+        <v>10</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.559891783632338</v>
+      </c>
+      <c r="H9" t="n">
+        <v>141024</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C10" t="n">
+        <v>100</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" t="n">
+        <v>10</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.503271886147559</v>
+      </c>
+      <c r="H10" t="n">
+        <v>141000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4</v>
+      </c>
+      <c r="F11" t="n">
+        <v>10</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.492929871194065</v>
+      </c>
+      <c r="H11" t="n">
+        <v>141776</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C12" t="n">
+        <v>10</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" t="n">
+        <v>8</v>
+      </c>
+      <c r="F12" t="n">
+        <v>10</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.586684321053326</v>
+      </c>
+      <c r="H12" t="n">
+        <v>112108</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C13" t="n">
+        <v>100</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" t="n">
+        <v>8</v>
+      </c>
+      <c r="F13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.476102477870882</v>
+      </c>
+      <c r="H13" t="n">
+        <v>112784</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" t="n">
+        <v>8</v>
+      </c>
+      <c r="F14" t="n">
+        <v>10</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.484810600988567</v>
+      </c>
+      <c r="H14" t="n">
+        <v>112556</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C15" t="n">
+        <v>10</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" t="n">
+        <v>16</v>
+      </c>
+      <c r="F15" t="n">
+        <v>10</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.436959996819496</v>
+      </c>
+      <c r="H15" t="n">
+        <v>100296</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C16" t="n">
+        <v>100</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="n">
+        <v>16</v>
+      </c>
+      <c r="F16" t="n">
+        <v>10</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.486238960176706</v>
+      </c>
+      <c r="H16" t="n">
+        <v>100836</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" t="n">
+        <v>16</v>
+      </c>
+      <c r="F17" t="n">
+        <v>10</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.403249806724489</v>
+      </c>
+      <c r="H17" t="n">
+        <v>98240</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C18" t="n">
+        <v>10</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" t="n">
+        <v>32</v>
+      </c>
+      <c r="F18" t="n">
+        <v>10</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.421885753050447</v>
+      </c>
+      <c r="H18" t="n">
+        <v>99340</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C19" t="n">
+        <v>100</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" t="n">
+        <v>32</v>
+      </c>
+      <c r="F19" t="n">
+        <v>10</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.348577813245356</v>
+      </c>
+      <c r="H19" t="n">
+        <v>103384</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" t="n">
+        <v>32</v>
+      </c>
+      <c r="F20" t="n">
+        <v>10</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.375905064865947</v>
+      </c>
+      <c r="H20" t="n">
+        <v>103692</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C21" t="n">
+        <v>10</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="n">
+        <v>64</v>
+      </c>
+      <c r="F21" t="n">
+        <v>10</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.812522923573852</v>
+      </c>
+      <c r="H21" t="n">
+        <v>104784</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C22" t="n">
+        <v>100</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="n">
+        <v>64</v>
+      </c>
+      <c r="F22" t="n">
+        <v>10</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.728061988949776</v>
+      </c>
+      <c r="H22" t="n">
+        <v>99912</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" t="n">
+        <v>64</v>
+      </c>
+      <c r="F23" t="n">
+        <v>10</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1.795999243855476</v>
+      </c>
+      <c r="H23" t="n">
+        <v>100872</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C24" t="n">
+        <v>10</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" t="n">
+        <v>128</v>
+      </c>
+      <c r="F24" t="n">
+        <v>10</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2.084200019016862</v>
+      </c>
+      <c r="H24" t="n">
+        <v>88636</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C25" t="n">
+        <v>100</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" t="n">
+        <v>128</v>
+      </c>
+      <c r="F25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2.405821989290416</v>
+      </c>
+      <c r="H25" t="n">
+        <v>88540</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" t="n">
+        <v>128</v>
+      </c>
+      <c r="F26" t="n">
+        <v>10</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2.545591720379889</v>
+      </c>
+      <c r="H26" t="n">
+        <v>97724</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C27" t="n">
+        <v>10</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" t="n">
+        <v>256</v>
+      </c>
+      <c r="F27" t="n">
+        <v>10</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1.667964354157448</v>
+      </c>
+      <c r="H27" t="n">
+        <v>89908</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C28" t="n">
+        <v>100</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" t="n">
+        <v>256</v>
+      </c>
+      <c r="F28" t="n">
+        <v>10</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.656173065304756</v>
+      </c>
+      <c r="H28" t="n">
+        <v>91968</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" t="n">
+        <v>256</v>
+      </c>
+      <c r="F29" t="n">
+        <v>10</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1.677726699970663</v>
+      </c>
+      <c r="H29" t="n">
+        <v>109140</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C30" t="n">
+        <v>10</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" t="n">
+        <v>512</v>
+      </c>
+      <c r="F30" t="n">
+        <v>10</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2.094345185905695</v>
+      </c>
+      <c r="H30" t="n">
+        <v>94484</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C31" t="n">
+        <v>100</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" t="n">
+        <v>512</v>
+      </c>
+      <c r="F31" t="n">
+        <v>10</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2.104926686733961</v>
+      </c>
+      <c r="H31" t="n">
+        <v>98128</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" t="n">
+        <v>512</v>
+      </c>
+      <c r="F32" t="n">
+        <v>10</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2.163337107747793</v>
+      </c>
+      <c r="H32" t="n">
+        <v>134180</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C33" t="n">
+        <v>10</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1024</v>
+      </c>
+      <c r="F33" t="n">
+        <v>10</v>
+      </c>
+      <c r="G33" t="n">
+        <v>3.025190380401909</v>
+      </c>
+      <c r="H33" t="n">
+        <v>107904</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C34" t="n">
+        <v>100</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1024</v>
+      </c>
+      <c r="F34" t="n">
+        <v>10</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2.981570299714804</v>
+      </c>
+      <c r="H34" t="n">
+        <v>115236</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1024</v>
+      </c>
+      <c r="F35" t="n">
+        <v>10</v>
+      </c>
+      <c r="G35" t="n">
+        <v>3.083353739231825</v>
+      </c>
+      <c r="H35" t="n">
+        <v>186152</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C36" t="n">
+        <v>10</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2</v>
+      </c>
+      <c r="E36" t="n">
+        <v>2048</v>
+      </c>
+      <c r="F36" t="n">
+        <v>10</v>
+      </c>
+      <c r="G36" t="n">
+        <v>5.172204298898578</v>
+      </c>
+      <c r="H36" t="n">
+        <v>136800</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C37" t="n">
+        <v>100</v>
+      </c>
+      <c r="D37" t="n">
+        <v>2</v>
+      </c>
+      <c r="E37" t="n">
+        <v>2048</v>
+      </c>
+      <c r="F37" t="n">
+        <v>10</v>
+      </c>
+      <c r="G37" t="n">
+        <v>5.233846741728485</v>
+      </c>
+      <c r="H37" t="n">
+        <v>150924</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D38" t="n">
+        <v>2</v>
+      </c>
+      <c r="E38" t="n">
+        <v>2048</v>
+      </c>
+      <c r="F38" t="n">
+        <v>10</v>
+      </c>
+      <c r="G38" t="n">
+        <v>5.54295042809099</v>
+      </c>
+      <c r="H38" t="n">
+        <v>294624</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C39" t="n">
+        <v>10</v>
+      </c>
+      <c r="D39" t="n">
+        <v>2</v>
+      </c>
+      <c r="E39" t="n">
+        <v>4096</v>
+      </c>
+      <c r="F39" t="n">
+        <v>10</v>
+      </c>
+      <c r="G39" t="n">
+        <v>9.302577997557819</v>
+      </c>
+      <c r="H39" t="n">
+        <v>189460</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C40" t="n">
+        <v>100</v>
+      </c>
+      <c r="D40" t="n">
+        <v>2</v>
+      </c>
+      <c r="E40" t="n">
+        <v>4096</v>
+      </c>
+      <c r="F40" t="n">
+        <v>10</v>
+      </c>
+      <c r="G40" t="n">
+        <v>9.258276352658868</v>
+      </c>
+      <c r="H40" t="n">
+        <v>219368</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D41" t="n">
+        <v>2</v>
+      </c>
+      <c r="E41" t="n">
+        <v>4096</v>
+      </c>
+      <c r="F41" t="n">
+        <v>10</v>
+      </c>
+      <c r="G41" t="n">
+        <v>9.770055879838765</v>
+      </c>
+      <c r="H41" t="n">
+        <v>506564</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C42" t="n">
+        <v>10</v>
+      </c>
+      <c r="D42" t="n">
+        <v>2</v>
+      </c>
+      <c r="E42" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F42" t="n">
+        <v>10</v>
+      </c>
+      <c r="G42" t="n">
+        <v>17.53386188019067</v>
+      </c>
+      <c r="H42" t="n">
+        <v>298528</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C43" t="n">
+        <v>100</v>
+      </c>
+      <c r="D43" t="n">
+        <v>2</v>
+      </c>
+      <c r="E43" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F43" t="n">
+        <v>10</v>
+      </c>
+      <c r="G43" t="n">
+        <v>17.47002328746021</v>
+      </c>
+      <c r="H43" t="n">
+        <v>356352</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D44" t="n">
+        <v>2</v>
+      </c>
+      <c r="E44" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F44" t="n">
+        <v>10</v>
+      </c>
+      <c r="G44" t="n">
+        <v>18.79519937559962</v>
+      </c>
+      <c r="H44" t="n">
+        <v>932540</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C45" t="n">
+        <v>10</v>
+      </c>
+      <c r="D45" t="n">
+        <v>2</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" t="n">
+        <v>10</v>
+      </c>
+      <c r="G45" t="n">
+        <v>1.772866178303957</v>
+      </c>
+      <c r="H45" t="n">
+        <v>316508</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C46" t="n">
+        <v>100</v>
+      </c>
+      <c r="D46" t="n">
+        <v>2</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" t="n">
+        <v>10</v>
+      </c>
+      <c r="G46" t="n">
+        <v>1.710867948830128</v>
+      </c>
+      <c r="H46" t="n">
+        <v>317076</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D47" t="n">
+        <v>2</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" t="n">
+        <v>10</v>
+      </c>
+      <c r="G47" t="n">
+        <v>1.699168330058455</v>
+      </c>
+      <c r="H47" t="n">
+        <v>317256</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C48" t="n">
+        <v>10</v>
+      </c>
+      <c r="D48" t="n">
+        <v>2</v>
+      </c>
+      <c r="E48" t="n">
+        <v>2</v>
+      </c>
+      <c r="F48" t="n">
+        <v>10</v>
+      </c>
+      <c r="G48" t="n">
+        <v>1.742422731593251</v>
+      </c>
+      <c r="H48" t="n">
+        <v>200068</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C49" t="n">
+        <v>100</v>
+      </c>
+      <c r="D49" t="n">
+        <v>2</v>
+      </c>
+      <c r="E49" t="n">
+        <v>2</v>
+      </c>
+      <c r="F49" t="n">
+        <v>10</v>
+      </c>
+      <c r="G49" t="n">
+        <v>1.702737042680383</v>
+      </c>
+      <c r="H49" t="n">
+        <v>199744</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D50" t="n">
+        <v>2</v>
+      </c>
+      <c r="E50" t="n">
+        <v>2</v>
+      </c>
+      <c r="F50" t="n">
+        <v>10</v>
+      </c>
+      <c r="G50" t="n">
+        <v>1.737075144425035</v>
+      </c>
+      <c r="H50" t="n">
+        <v>199736</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C51" t="n">
+        <v>10</v>
+      </c>
+      <c r="D51" t="n">
+        <v>2</v>
+      </c>
+      <c r="E51" t="n">
+        <v>4</v>
+      </c>
+      <c r="F51" t="n">
+        <v>10</v>
+      </c>
+      <c r="G51" t="n">
+        <v>1.541765429079533</v>
+      </c>
+      <c r="H51" t="n">
+        <v>140868</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C52" t="n">
+        <v>100</v>
+      </c>
+      <c r="D52" t="n">
+        <v>2</v>
+      </c>
+      <c r="E52" t="n">
+        <v>4</v>
+      </c>
+      <c r="F52" t="n">
+        <v>10</v>
+      </c>
+      <c r="G52" t="n">
+        <v>1.488545279949903</v>
+      </c>
+      <c r="H52" t="n">
+        <v>141008</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C53" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D53" t="n">
+        <v>2</v>
+      </c>
+      <c r="E53" t="n">
+        <v>4</v>
+      </c>
+      <c r="F53" t="n">
+        <v>10</v>
+      </c>
+      <c r="G53" t="n">
+        <v>1.498334936797619</v>
+      </c>
+      <c r="H53" t="n">
+        <v>141380</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C54" t="n">
+        <v>10</v>
+      </c>
+      <c r="D54" t="n">
+        <v>2</v>
+      </c>
+      <c r="E54" t="n">
+        <v>8</v>
+      </c>
+      <c r="F54" t="n">
+        <v>10</v>
+      </c>
+      <c r="G54" t="n">
+        <v>1.567122159525752</v>
+      </c>
+      <c r="H54" t="n">
+        <v>111900</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C55" t="n">
+        <v>100</v>
+      </c>
+      <c r="D55" t="n">
+        <v>2</v>
+      </c>
+      <c r="E55" t="n">
+        <v>8</v>
+      </c>
+      <c r="F55" t="n">
+        <v>10</v>
+      </c>
+      <c r="G55" t="n">
+        <v>1.473392548039556</v>
+      </c>
+      <c r="H55" t="n">
+        <v>110728</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C56" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D56" t="n">
+        <v>2</v>
+      </c>
+      <c r="E56" t="n">
+        <v>8</v>
+      </c>
+      <c r="F56" t="n">
+        <v>10</v>
+      </c>
+      <c r="G56" t="n">
+        <v>1.535733828321099</v>
+      </c>
+      <c r="H56" t="n">
+        <v>111368</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C57" t="n">
+        <v>10</v>
+      </c>
+      <c r="D57" t="n">
+        <v>2</v>
+      </c>
+      <c r="E57" t="n">
+        <v>16</v>
+      </c>
+      <c r="F57" t="n">
+        <v>10</v>
+      </c>
+      <c r="G57" t="n">
+        <v>1.417526779696345</v>
+      </c>
+      <c r="H57" t="n">
+        <v>100696</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C58" t="n">
+        <v>100</v>
+      </c>
+      <c r="D58" t="n">
+        <v>2</v>
+      </c>
+      <c r="E58" t="n">
+        <v>16</v>
+      </c>
+      <c r="F58" t="n">
+        <v>10</v>
+      </c>
+      <c r="G58" t="n">
+        <v>1.35969434119761</v>
+      </c>
+      <c r="H58" t="n">
+        <v>97924</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D59" t="n">
+        <v>2</v>
+      </c>
+      <c r="E59" t="n">
+        <v>16</v>
+      </c>
+      <c r="F59" t="n">
+        <v>10</v>
+      </c>
+      <c r="G59" t="n">
+        <v>1.402023233473301</v>
+      </c>
+      <c r="H59" t="n">
+        <v>99756</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C60" t="n">
+        <v>10</v>
+      </c>
+      <c r="D60" t="n">
+        <v>2</v>
+      </c>
+      <c r="E60" t="n">
+        <v>32</v>
+      </c>
+      <c r="F60" t="n">
+        <v>10</v>
+      </c>
+      <c r="G60" t="n">
+        <v>1.425094434991479</v>
+      </c>
+      <c r="H60" t="n">
+        <v>105488</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C61" t="n">
+        <v>100</v>
+      </c>
+      <c r="D61" t="n">
+        <v>2</v>
+      </c>
+      <c r="E61" t="n">
+        <v>32</v>
+      </c>
+      <c r="F61" t="n">
+        <v>10</v>
+      </c>
+      <c r="G61" t="n">
+        <v>1.350117551162839</v>
+      </c>
+      <c r="H61" t="n">
+        <v>101568</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C62" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D62" t="n">
+        <v>2</v>
+      </c>
+      <c r="E62" t="n">
+        <v>32</v>
+      </c>
+      <c r="F62" t="n">
+        <v>10</v>
+      </c>
+      <c r="G62" t="n">
+        <v>1.507360253483057</v>
+      </c>
+      <c r="H62" t="n">
+        <v>93952</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C63" t="n">
+        <v>10</v>
+      </c>
+      <c r="D63" t="n">
+        <v>2</v>
+      </c>
+      <c r="E63" t="n">
+        <v>64</v>
+      </c>
+      <c r="F63" t="n">
+        <v>10</v>
+      </c>
+      <c r="G63" t="n">
+        <v>1.774707827717066</v>
+      </c>
+      <c r="H63" t="n">
+        <v>103292</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C64" t="n">
+        <v>100</v>
+      </c>
+      <c r="D64" t="n">
+        <v>2</v>
+      </c>
+      <c r="E64" t="n">
+        <v>64</v>
+      </c>
+      <c r="F64" t="n">
+        <v>10</v>
+      </c>
+      <c r="G64" t="n">
+        <v>1.720007238909602</v>
+      </c>
+      <c r="H64" t="n">
+        <v>100712</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D65" t="n">
+        <v>2</v>
+      </c>
+      <c r="E65" t="n">
+        <v>64</v>
+      </c>
+      <c r="F65" t="n">
+        <v>10</v>
+      </c>
+      <c r="G65" t="n">
+        <v>1.774926537647843</v>
+      </c>
+      <c r="H65" t="n">
+        <v>95468</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C66" t="n">
+        <v>10</v>
+      </c>
+      <c r="D66" t="n">
+        <v>2</v>
+      </c>
+      <c r="E66" t="n">
+        <v>128</v>
+      </c>
+      <c r="F66" t="n">
+        <v>10</v>
+      </c>
+      <c r="G66" t="n">
+        <v>2.544224170967937</v>
+      </c>
+      <c r="H66" t="n">
+        <v>88492</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C67" t="n">
+        <v>100</v>
+      </c>
+      <c r="D67" t="n">
+        <v>2</v>
+      </c>
+      <c r="E67" t="n">
+        <v>128</v>
+      </c>
+      <c r="F67" t="n">
+        <v>10</v>
+      </c>
+      <c r="G67" t="n">
+        <v>2.368753237649798</v>
+      </c>
+      <c r="H67" t="n">
+        <v>89432</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C68" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D68" t="n">
+        <v>2</v>
+      </c>
+      <c r="E68" t="n">
+        <v>128</v>
+      </c>
+      <c r="F68" t="n">
+        <v>10</v>
+      </c>
+      <c r="G68" t="n">
+        <v>2.348510451614857</v>
+      </c>
+      <c r="H68" t="n">
+        <v>97252</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C69" t="n">
+        <v>10</v>
+      </c>
+      <c r="D69" t="n">
+        <v>2</v>
+      </c>
+      <c r="E69" t="n">
+        <v>256</v>
+      </c>
+      <c r="F69" t="n">
+        <v>10</v>
+      </c>
+      <c r="G69" t="n">
+        <v>1.698470985516906</v>
+      </c>
+      <c r="H69" t="n">
+        <v>90040</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>68</v>
+      </c>
+      <c r="B70" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C70" t="n">
+        <v>100</v>
+      </c>
+      <c r="D70" t="n">
+        <v>2</v>
+      </c>
+      <c r="E70" t="n">
+        <v>256</v>
+      </c>
+      <c r="F70" t="n">
+        <v>10</v>
+      </c>
+      <c r="G70" t="n">
+        <v>1.636501170694828</v>
+      </c>
+      <c r="H70" t="n">
+        <v>92512</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C71" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D71" t="n">
+        <v>2</v>
+      </c>
+      <c r="E71" t="n">
+        <v>256</v>
+      </c>
+      <c r="F71" t="n">
+        <v>10</v>
+      </c>
+      <c r="G71" t="n">
+        <v>1.674029560759664</v>
+      </c>
+      <c r="H71" t="n">
+        <v>109068</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C72" t="n">
+        <v>10</v>
+      </c>
+      <c r="D72" t="n">
+        <v>2</v>
+      </c>
+      <c r="E72" t="n">
+        <v>512</v>
+      </c>
+      <c r="F72" t="n">
+        <v>10</v>
+      </c>
+      <c r="G72" t="n">
+        <v>2.134681025519967</v>
+      </c>
+      <c r="H72" t="n">
+        <v>94516</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C73" t="n">
+        <v>100</v>
+      </c>
+      <c r="D73" t="n">
+        <v>2</v>
+      </c>
+      <c r="E73" t="n">
+        <v>512</v>
+      </c>
+      <c r="F73" t="n">
+        <v>10</v>
+      </c>
+      <c r="G73" t="n">
+        <v>2.117395238950849</v>
+      </c>
+      <c r="H73" t="n">
+        <v>98324</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C74" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D74" t="n">
+        <v>2</v>
+      </c>
+      <c r="E74" t="n">
+        <v>512</v>
+      </c>
+      <c r="F74" t="n">
+        <v>10</v>
+      </c>
+      <c r="G74" t="n">
+        <v>2.155463906005025</v>
+      </c>
+      <c r="H74" t="n">
+        <v>134456</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C75" t="n">
+        <v>10</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1024</v>
+      </c>
+      <c r="F75" t="n">
+        <v>10</v>
+      </c>
+      <c r="G75" t="n">
+        <v>3.034335669130087</v>
+      </c>
+      <c r="H75" t="n">
+        <v>107580</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C76" t="n">
+        <v>100</v>
+      </c>
+      <c r="D76" t="n">
+        <v>2</v>
+      </c>
+      <c r="E76" t="n">
+        <v>1024</v>
+      </c>
+      <c r="F76" t="n">
+        <v>10</v>
+      </c>
+      <c r="G76" t="n">
+        <v>3.00251585431397</v>
+      </c>
+      <c r="H76" t="n">
+        <v>115056</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>75</v>
+      </c>
+      <c r="B77" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C77" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D77" t="n">
+        <v>2</v>
+      </c>
+      <c r="E77" t="n">
+        <v>1024</v>
+      </c>
+      <c r="F77" t="n">
+        <v>10</v>
+      </c>
+      <c r="G77" t="n">
+        <v>3.139016849920154</v>
+      </c>
+      <c r="H77" t="n">
+        <v>186872</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>76</v>
+      </c>
+      <c r="B78" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C78" t="n">
+        <v>10</v>
+      </c>
+      <c r="D78" t="n">
+        <v>2</v>
+      </c>
+      <c r="E78" t="n">
+        <v>2048</v>
+      </c>
+      <c r="F78" t="n">
+        <v>10</v>
+      </c>
+      <c r="G78" t="n">
+        <v>5.263988476246595</v>
+      </c>
+      <c r="H78" t="n">
+        <v>136988</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>77</v>
+      </c>
+      <c r="B79" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C79" t="n">
+        <v>100</v>
+      </c>
+      <c r="D79" t="n">
+        <v>2</v>
+      </c>
+      <c r="E79" t="n">
+        <v>2048</v>
+      </c>
+      <c r="F79" t="n">
+        <v>10</v>
+      </c>
+      <c r="G79" t="n">
+        <v>5.249896991997957</v>
+      </c>
+      <c r="H79" t="n">
+        <v>150956</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>78</v>
+      </c>
+      <c r="B80" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C80" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D80" t="n">
+        <v>2</v>
+      </c>
+      <c r="E80" t="n">
+        <v>2048</v>
+      </c>
+      <c r="F80" t="n">
+        <v>10</v>
+      </c>
+      <c r="G80" t="n">
+        <v>5.453855097293854</v>
+      </c>
+      <c r="H80" t="n">
+        <v>294652</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>79</v>
+      </c>
+      <c r="B81" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C81" t="n">
+        <v>10</v>
+      </c>
+      <c r="D81" t="n">
+        <v>2</v>
+      </c>
+      <c r="E81" t="n">
+        <v>4096</v>
+      </c>
+      <c r="F81" t="n">
+        <v>10</v>
+      </c>
+      <c r="G81" t="n">
+        <v>9.344677355140448</v>
+      </c>
+      <c r="H81" t="n">
+        <v>189960</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>80</v>
+      </c>
+      <c r="B82" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C82" t="n">
+        <v>100</v>
+      </c>
+      <c r="D82" t="n">
+        <v>2</v>
+      </c>
+      <c r="E82" t="n">
+        <v>4096</v>
+      </c>
+      <c r="F82" t="n">
+        <v>10</v>
+      </c>
+      <c r="G82" t="n">
+        <v>9.066703902557492</v>
+      </c>
+      <c r="H82" t="n">
+        <v>219116</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>81</v>
+      </c>
+      <c r="B83" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C83" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D83" t="n">
+        <v>2</v>
+      </c>
+      <c r="E83" t="n">
+        <v>4096</v>
+      </c>
+      <c r="F83" t="n">
+        <v>10</v>
+      </c>
+      <c r="G83" t="n">
+        <v>9.619278155267239</v>
+      </c>
+      <c r="H83" t="n">
+        <v>506660</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>82</v>
+      </c>
+      <c r="B84" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C84" t="n">
+        <v>10</v>
+      </c>
+      <c r="D84" t="n">
+        <v>2</v>
+      </c>
+      <c r="E84" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F84" t="n">
+        <v>10</v>
+      </c>
+      <c r="G84" t="n">
+        <v>17.23823546245694</v>
+      </c>
+      <c r="H84" t="n">
+        <v>298868</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>83</v>
+      </c>
+      <c r="B85" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C85" t="n">
+        <v>100</v>
+      </c>
+      <c r="D85" t="n">
+        <v>2</v>
+      </c>
+      <c r="E85" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F85" t="n">
+        <v>10</v>
+      </c>
+      <c r="G85" t="n">
+        <v>17.2722056210041</v>
+      </c>
+      <c r="H85" t="n">
+        <v>356392</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>84</v>
+      </c>
+      <c r="B86" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C86" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D86" t="n">
+        <v>2</v>
+      </c>
+      <c r="E86" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F86" t="n">
+        <v>10</v>
+      </c>
+      <c r="G86" t="n">
+        <v>18.49684765376151</v>
+      </c>
+      <c r="H86" t="n">
+        <v>932600</v>
+      </c>
+    </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H2"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>